--- a/analyst/Franzi/rmonize/data_proc_elem/DPE_NAKO_FRANZI.xlsx
+++ b/analyst/Franzi/rmonize/data_proc_elem/DPE_NAKO_FRANZI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Franzi\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13952177-A59D-40DF-9458-5263F235724B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE6FEBE-F65D-4B85-B661-900D07BBE46C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1698,21 +1698,18 @@
         <v>13</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>256</v>
+      <c r="G17" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
@@ -1725,18 +1722,21 @@
       <c r="D18" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>273</v>
+      <c r="F18" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
@@ -3043,7 +3043,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="73" spans="2:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>154</v>
       </c>

--- a/analyst/Franzi/rmonize/data_proc_elem/DPE_NAKO_FRANZI.xlsx
+++ b/analyst/Franzi/rmonize/data_proc_elem/DPE_NAKO_FRANZI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Franzi\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE6FEBE-F65D-4B85-B661-900D07BBE46C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7A33D9-992C-4ACD-94BE-E2239DB89BE4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -814,9 +814,6 @@
     <t>a_ui_m03</t>
   </si>
   <si>
-    <t>a_ui_f0401</t>
-  </si>
-  <si>
     <t>operation</t>
   </si>
   <si>
@@ -845,6 +842,9 @@
   </si>
   <si>
     <t>a_ui_f070100;a_ui_f070101;a_ui_f070103</t>
+  </si>
+  <si>
+    <t>a_ui_m04</t>
   </si>
 </sst>
 </file>
@@ -1330,17 +1330,17 @@
         <v>13</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1354,17 +1354,17 @@
         <v>13</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1378,17 +1378,17 @@
         <v>13</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1430,17 +1430,17 @@
         <v>13</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1454,17 +1454,17 @@
         <v>13</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1478,17 +1478,17 @@
         <v>13</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1502,17 +1502,17 @@
         <v>13</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1526,17 +1526,17 @@
         <v>13</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1550,17 +1550,17 @@
         <v>13</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1574,17 +1574,17 @@
         <v>13</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1598,17 +1598,17 @@
         <v>13</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1622,17 +1622,17 @@
         <v>13</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1674,17 +1674,17 @@
         <v>13</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
@@ -1698,18 +1698,21 @@
         <v>13</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="G17" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>273</v>
+      <c r="F17" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="I17" s="7"/>
-      <c r="J17" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>273</v>
+      <c r="J17" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
@@ -1722,21 +1725,19 @@
       <c r="D18" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>254</v>
+      <c r="F18" s="3"/>
+      <c r="G18" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>272</v>
       </c>
       <c r="I18" s="2"/>
-      <c r="J18" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>256</v>
+      <c r="J18" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
@@ -1750,17 +1751,17 @@
         <v>13</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
@@ -1774,17 +1775,17 @@
         <v>13</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
@@ -1798,17 +1799,17 @@
         <v>13</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
@@ -1822,17 +1823,17 @@
         <v>13</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
@@ -1846,17 +1847,17 @@
         <v>13</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
@@ -1870,17 +1871,17 @@
         <v>13</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
@@ -1894,17 +1895,17 @@
         <v>13</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
@@ -1918,17 +1919,17 @@
         <v>13</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
@@ -1942,17 +1943,17 @@
         <v>13</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
@@ -1966,17 +1967,17 @@
         <v>13</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I28" s="7"/>
       <c r="J28" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
@@ -1990,17 +1991,17 @@
         <v>13</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I29" s="7"/>
       <c r="J29" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
@@ -2014,17 +2015,17 @@
         <v>13</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
@@ -2038,17 +2039,17 @@
         <v>13</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I31" s="7"/>
       <c r="J31" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
@@ -2062,17 +2063,17 @@
         <v>13</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I32" s="7"/>
       <c r="J32" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
@@ -2086,17 +2087,17 @@
         <v>13</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I33" s="7"/>
       <c r="J33" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
@@ -2110,17 +2111,17 @@
         <v>13</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
@@ -2134,17 +2135,17 @@
         <v>13</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
@@ -2158,17 +2159,17 @@
         <v>13</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
@@ -2182,17 +2183,17 @@
         <v>13</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
@@ -2206,17 +2207,17 @@
         <v>13</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
@@ -2230,17 +2231,17 @@
         <v>13</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
@@ -2254,17 +2255,17 @@
         <v>13</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
@@ -2278,17 +2279,17 @@
         <v>13</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I41" s="7"/>
       <c r="J41" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
@@ -2302,17 +2303,17 @@
         <v>13</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I42" s="7"/>
       <c r="J42" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="2:11" ht="45" x14ac:dyDescent="0.25">
@@ -2327,20 +2328,20 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G43" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2" t="s">
         <v>255</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
@@ -2354,17 +2355,17 @@
         <v>13</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
@@ -2378,17 +2379,17 @@
         <v>13</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I45" s="7"/>
       <c r="J45" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
@@ -2402,17 +2403,17 @@
         <v>13</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I46" s="7"/>
       <c r="J46" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -2426,17 +2427,17 @@
         <v>13</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I47" s="7"/>
       <c r="J47" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
@@ -2450,17 +2451,17 @@
         <v>13</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I48" s="7"/>
       <c r="J48" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
@@ -2474,17 +2475,17 @@
         <v>13</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
@@ -2498,17 +2499,17 @@
         <v>13</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I50" s="7"/>
       <c r="J50" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
@@ -2522,17 +2523,17 @@
         <v>13</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I51" s="7"/>
       <c r="J51" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
@@ -2546,17 +2547,17 @@
         <v>13</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I52" s="7"/>
       <c r="J52" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
@@ -2570,17 +2571,17 @@
         <v>13</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I53" s="7"/>
       <c r="J53" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
@@ -2594,17 +2595,17 @@
         <v>13</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I54" s="7"/>
       <c r="J54" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
@@ -2618,17 +2619,17 @@
         <v>13</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I55" s="7"/>
       <c r="J55" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
@@ -2642,17 +2643,17 @@
         <v>13</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I56" s="7"/>
       <c r="J56" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
@@ -2666,17 +2667,17 @@
         <v>13</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I57" s="7"/>
       <c r="J57" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
@@ -2691,7 +2692,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>254</v>
@@ -2718,17 +2719,17 @@
         <v>13</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
@@ -2742,17 +2743,17 @@
         <v>13</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I60" s="7"/>
       <c r="J60" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
@@ -2766,17 +2767,17 @@
         <v>13</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I61" s="7"/>
       <c r="J61" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
@@ -2790,17 +2791,17 @@
         <v>13</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I62" s="7"/>
       <c r="J62" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
@@ -2814,17 +2815,17 @@
         <v>13</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I63" s="7"/>
       <c r="J63" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
@@ -2838,17 +2839,17 @@
         <v>13</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I64" s="7"/>
       <c r="J64" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
@@ -2862,17 +2863,17 @@
         <v>13</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I65" s="7"/>
       <c r="J65" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
@@ -2886,17 +2887,17 @@
         <v>13</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I66" s="7"/>
       <c r="J66" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
@@ -2910,17 +2911,17 @@
         <v>13</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I67" s="7"/>
       <c r="J67" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
@@ -2934,17 +2935,17 @@
         <v>13</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I68" s="7"/>
       <c r="J68" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
@@ -2958,17 +2959,17 @@
         <v>13</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I69" s="7"/>
       <c r="J69" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
@@ -2982,17 +2983,17 @@
         <v>13</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I70" s="7"/>
       <c r="J70" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
@@ -3006,17 +3007,17 @@
         <v>13</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I71" s="7"/>
       <c r="J71" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
@@ -3030,17 +3031,17 @@
         <v>13</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I72" s="7"/>
       <c r="J72" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
@@ -3082,17 +3083,17 @@
         <v>13</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
@@ -3106,17 +3107,17 @@
         <v>13</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I75" s="7"/>
       <c r="J75" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
@@ -3130,17 +3131,17 @@
         <v>13</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
@@ -3154,17 +3155,17 @@
         <v>13</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I77" s="7"/>
       <c r="J77" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
@@ -3178,17 +3179,17 @@
         <v>13</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I78" s="7"/>
       <c r="J78" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
@@ -3202,17 +3203,17 @@
         <v>13</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I79" s="7"/>
       <c r="J79" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
@@ -3226,17 +3227,17 @@
         <v>13</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I80" s="7"/>
       <c r="J80" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
@@ -3250,17 +3251,17 @@
         <v>13</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I81" s="7"/>
       <c r="J81" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
@@ -3302,17 +3303,17 @@
         <v>13</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I83" s="7"/>
       <c r="J83" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
@@ -3326,17 +3327,17 @@
         <v>13</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I84" s="7"/>
       <c r="J84" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
@@ -3350,17 +3351,17 @@
         <v>13</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I85" s="7"/>
       <c r="J85" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
@@ -3430,17 +3431,17 @@
         <v>13</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I88" s="7"/>
       <c r="J88" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
@@ -3455,7 +3456,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>254</v>
@@ -3483,7 +3484,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>254</v>
@@ -3510,17 +3511,17 @@
         <v>13</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I91" s="7"/>
       <c r="J91" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
@@ -3534,17 +3535,17 @@
         <v>13</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I92" s="7"/>
       <c r="J92" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
@@ -3558,17 +3559,17 @@
         <v>13</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I93" s="7"/>
       <c r="J93" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
@@ -3582,17 +3583,17 @@
         <v>13</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I94" s="7"/>
       <c r="J94" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.25">
@@ -3606,17 +3607,17 @@
         <v>13</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I95" s="7"/>
       <c r="J95" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
@@ -3630,17 +3631,17 @@
         <v>13</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I96" s="7"/>
       <c r="J96" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
@@ -3654,17 +3655,17 @@
         <v>13</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I97" s="7"/>
       <c r="J97" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
@@ -3678,17 +3679,17 @@
         <v>13</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I98" s="7"/>
       <c r="J98" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K98" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
@@ -3702,17 +3703,17 @@
         <v>13</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I99" s="7"/>
       <c r="J99" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
@@ -3726,17 +3727,17 @@
         <v>13</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I100" s="7"/>
       <c r="J100" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
@@ -3750,17 +3751,17 @@
         <v>13</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I101" s="7"/>
       <c r="J101" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
@@ -3774,17 +3775,17 @@
         <v>13</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I102" s="7"/>
       <c r="J102" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
@@ -3798,17 +3799,17 @@
         <v>13</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
@@ -3822,17 +3823,17 @@
         <v>13</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I104" s="7"/>
       <c r="J104" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
@@ -3846,17 +3847,17 @@
         <v>13</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I105" s="7"/>
       <c r="J105" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
@@ -3870,17 +3871,17 @@
         <v>13</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I106" s="7"/>
       <c r="J106" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
@@ -3894,17 +3895,17 @@
         <v>13</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I107" s="7"/>
       <c r="J107" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
@@ -3918,17 +3919,17 @@
         <v>13</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I108" s="7"/>
       <c r="J108" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
@@ -3942,17 +3943,17 @@
         <v>13</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I109" s="7"/>
       <c r="J109" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.25">
@@ -3966,17 +3967,17 @@
         <v>13</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I110" s="7"/>
       <c r="J110" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.25">
@@ -3990,17 +3991,17 @@
         <v>13</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I111" s="7"/>
       <c r="J111" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.25">
@@ -4014,17 +4015,17 @@
         <v>13</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I112" s="7"/>
       <c r="J112" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
@@ -4038,17 +4039,17 @@
         <v>13</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I113" s="7"/>
       <c r="J113" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
@@ -4062,17 +4063,17 @@
         <v>13</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H114" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I114" s="7"/>
       <c r="J114" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.25">
@@ -4086,17 +4087,17 @@
         <v>13</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H115" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I115" s="7"/>
       <c r="J115" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
@@ -4110,17 +4111,17 @@
         <v>13</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H116" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I116" s="7"/>
       <c r="J116" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
@@ -4134,17 +4135,17 @@
         <v>13</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H117" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I117" s="7"/>
       <c r="J117" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
@@ -4184,17 +4185,17 @@
         <v>13</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H119" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I119" s="7"/>
       <c r="J119" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K119" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
@@ -4208,17 +4209,17 @@
         <v>13</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H120" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I120" s="7"/>
       <c r="J120" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K120" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
@@ -4233,10 +4234,10 @@
       </c>
       <c r="E121" s="4"/>
       <c r="F121" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="G121" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="H121" s="4">
         <v>6</v>
